--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CLUB OURENSE BALONCESTO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CLUB OURENSE BALONCESTO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>32.8603</v>
+        <v>33.3195</v>
       </c>
       <c r="E2" t="n">
-        <v>22.548</v>
+        <v>37.0567</v>
       </c>
       <c r="F2" t="n">
-        <v>10.3121</v>
+        <v>-3.7373</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9925</v>
+        <v>28.252</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.459000000000001</v>
+        <v>22.1477</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4511</v>
+        <v>6.104200000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>5.967000000000001</v>
+        <v>40.2765</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7383</v>
+        <v>30.1451</v>
       </c>
       <c r="L2" t="n">
-        <v>4.2286</v>
+        <v>10.1313</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.975</v>
+        <v>-12.0244</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.196899999999999</v>
+        <v>-7.9973</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2221999999999996</v>
+        <v>-4.027</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0875</v>
+        <v>14.3554</v>
       </c>
       <c r="Q2" t="n">
-        <v>-19.1403</v>
+        <v>-30.8857</v>
       </c>
       <c r="R2" t="n">
-        <v>20.228</v>
+        <v>45.2411</v>
       </c>
       <c r="S2" t="n">
-        <v>23.5222</v>
+        <v>11.1006</v>
       </c>
       <c r="T2" t="n">
-        <v>19.2536</v>
+        <v>10.5511</v>
       </c>
       <c r="U2" t="n">
-        <v>4.2686</v>
+        <v>0.5491999999999998</v>
       </c>
       <c r="V2" t="n">
-        <v>6.2582</v>
+        <v>-20.3887</v>
       </c>
       <c r="W2" t="n">
-        <v>16.4674</v>
+        <v>17.1148</v>
       </c>
       <c r="X2" t="n">
-        <v>-10.2095</v>
+        <v>-37.5037</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>21.8757</v>
+        <v>21.5608</v>
       </c>
       <c r="E3" t="n">
-        <v>27.1497</v>
+        <v>12.9077</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.2737</v>
+        <v>8.6532</v>
       </c>
       <c r="G3" t="n">
-        <v>28.252</v>
+        <v>1.9925</v>
       </c>
       <c r="H3" t="n">
-        <v>22.1477</v>
+        <v>-2.459000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>6.104200000000001</v>
+        <v>4.4511</v>
       </c>
       <c r="J3" t="n">
-        <v>40.2765</v>
+        <v>5.967000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>30.1451</v>
+        <v>1.7383</v>
       </c>
       <c r="L3" t="n">
-        <v>10.1313</v>
+        <v>4.2286</v>
       </c>
       <c r="M3" t="n">
-        <v>-12.0244</v>
+        <v>-3.975</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.9973</v>
+        <v>-4.196899999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.027</v>
+        <v>0.2221999999999996</v>
       </c>
       <c r="P3" t="n">
-        <v>14.3554</v>
+        <v>1.0875</v>
       </c>
       <c r="Q3" t="n">
-        <v>-30.8857</v>
+        <v>-19.1403</v>
       </c>
       <c r="R3" t="n">
-        <v>45.2411</v>
+        <v>20.228</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3429999999999996</v>
+        <v>12.2231</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6445</v>
+        <v>9.6136</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9872999999999998</v>
+        <v>2.6095</v>
       </c>
       <c r="V3" t="n">
-        <v>-20.3887</v>
+        <v>6.2582</v>
       </c>
       <c r="W3" t="n">
-        <v>17.1148</v>
+        <v>16.4674</v>
       </c>
       <c r="X3" t="n">
-        <v>-37.5037</v>
+        <v>-10.2095</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARBALLO</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>15.2424</v>
+        <v>20.8677</v>
       </c>
       <c r="E4" t="n">
-        <v>20.8655</v>
+        <v>33.1754</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.6235</v>
+        <v>-12.3077</v>
       </c>
       <c r="G4" t="n">
-        <v>-15.216</v>
+        <v>17.1242</v>
       </c>
       <c r="H4" t="n">
-        <v>-8.174099999999999</v>
+        <v>-7.5001</v>
       </c>
       <c r="I4" t="n">
-        <v>-7.0423</v>
+        <v>24.6244</v>
       </c>
       <c r="J4" t="n">
-        <v>1.228200000000001</v>
+        <v>59.8297</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.8838</v>
+        <v>18.1386</v>
       </c>
       <c r="L4" t="n">
-        <v>4.112</v>
+        <v>41.6913</v>
       </c>
       <c r="M4" t="n">
-        <v>-16.4444</v>
+        <v>-42.7056</v>
       </c>
       <c r="N4" t="n">
-        <v>-5.2903</v>
+        <v>-25.6386</v>
       </c>
       <c r="O4" t="n">
-        <v>-11.1542</v>
+        <v>-17.067</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0876</v>
+        <v>-3.6977</v>
       </c>
       <c r="Q4" t="n">
-        <v>-24.3606</v>
+        <v>-59.8142</v>
       </c>
       <c r="R4" t="n">
-        <v>25.4478</v>
+        <v>56.1171</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1481</v>
+        <v>3.6697</v>
       </c>
       <c r="T4" t="n">
-        <v>4.1087</v>
+        <v>5.043799999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.9611</v>
+        <v>-1.374</v>
       </c>
       <c r="V4" t="n">
-        <v>27.2227</v>
+        <v>3.7715</v>
       </c>
       <c r="W4" t="n">
-        <v>39.889</v>
+        <v>28.1162</v>
       </c>
       <c r="X4" t="n">
-        <v>-12.6663</v>
+        <v>-24.3444</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>M. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>13.0792</v>
+        <v>19.1483</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8202</v>
+        <v>23.6053</v>
       </c>
       <c r="F5" t="n">
-        <v>7.2588</v>
+        <v>-4.456799999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.738</v>
+        <v>-15.216</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.5087</v>
+        <v>-8.174099999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1.771</v>
+        <v>-7.0423</v>
       </c>
       <c r="J5" t="n">
-        <v>10.2022</v>
+        <v>1.228200000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5854</v>
+        <v>-2.8838</v>
       </c>
       <c r="L5" t="n">
-        <v>6.6165</v>
+        <v>4.112</v>
       </c>
       <c r="M5" t="n">
-        <v>-13.94</v>
+        <v>-16.4444</v>
       </c>
       <c r="N5" t="n">
-        <v>-9.0937</v>
+        <v>-5.2903</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.8459</v>
+        <v>-11.1542</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001999999999992841</v>
+        <v>1.0876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-36.1058</v>
+        <v>-24.3606</v>
       </c>
       <c r="R5" t="n">
-        <v>36.1058</v>
+        <v>25.4478</v>
       </c>
       <c r="S5" t="n">
-        <v>40.8134</v>
+        <v>6.0541</v>
       </c>
       <c r="T5" t="n">
-        <v>26.0834</v>
+        <v>6.8487</v>
       </c>
       <c r="U5" t="n">
-        <v>14.7306</v>
+        <v>-0.7945</v>
       </c>
       <c r="V5" t="n">
-        <v>-23.9966</v>
+        <v>27.2227</v>
       </c>
       <c r="W5" t="n">
-        <v>5.6407</v>
+        <v>39.889</v>
       </c>
       <c r="X5" t="n">
-        <v>-29.6375</v>
+        <v>-12.6663</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>6.272000000000001</v>
+        <v>7.3443</v>
       </c>
       <c r="E6" t="n">
-        <v>18.7633</v>
+        <v>16.9427</v>
       </c>
       <c r="F6" t="n">
-        <v>-12.4913</v>
+        <v>-9.598899999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-17.4571</v>
@@ -922,13 +922,13 @@
         <v>57.2043</v>
       </c>
       <c r="S6" t="n">
-        <v>15.8555</v>
+        <v>16.9276</v>
       </c>
       <c r="T6" t="n">
-        <v>17.036</v>
+        <v>15.2154</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1802</v>
+        <v>1.7127</v>
       </c>
       <c r="V6" t="n">
         <v>-9.962199999999999</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>K. SMITH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>4.5091</v>
+        <v>5.125100000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>29.2791</v>
+        <v>1.3019</v>
       </c>
       <c r="F7" t="n">
-        <v>-24.7698</v>
+        <v>3.8233</v>
       </c>
       <c r="G7" t="n">
-        <v>-18.5102</v>
+        <v>-0.1555999999999998</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.736499999999999</v>
+        <v>-6.1992</v>
       </c>
       <c r="I7" t="n">
-        <v>-13.7741</v>
+        <v>6.0435</v>
       </c>
       <c r="J7" t="n">
-        <v>13.538</v>
+        <v>14.5056</v>
       </c>
       <c r="K7" t="n">
-        <v>10.9174</v>
+        <v>1.6645</v>
       </c>
       <c r="L7" t="n">
-        <v>2.6202</v>
+        <v>12.8411</v>
       </c>
       <c r="M7" t="n">
-        <v>-32.0488</v>
+        <v>-14.6612</v>
       </c>
       <c r="N7" t="n">
-        <v>-15.6538</v>
+        <v>-7.863700000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-16.395</v>
+        <v>-6.7975</v>
       </c>
       <c r="P7" t="n">
-        <v>-8.917899999999999</v>
+        <v>10.4404</v>
       </c>
       <c r="Q7" t="n">
-        <v>-45.8937</v>
+        <v>-18.7053</v>
       </c>
       <c r="R7" t="n">
-        <v>36.9757</v>
+        <v>29.146</v>
       </c>
       <c r="S7" t="n">
-        <v>35.1512</v>
+        <v>6.2737</v>
       </c>
       <c r="T7" t="n">
-        <v>32.9002</v>
+        <v>6.9605</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2507</v>
+        <v>-0.6866</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.213799999999999</v>
+        <v>-11.4331</v>
       </c>
       <c r="W7" t="n">
-        <v>28.7342</v>
+        <v>-1.4583</v>
       </c>
       <c r="X7" t="n">
-        <v>-31.9481</v>
+        <v>-9.9749</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. SMITH</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>2.6813</v>
+        <v>-6.440900000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9955999999999996</v>
+        <v>-6.4155</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6857</v>
+        <v>-0.0249999999999998</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1555999999999998</v>
+        <v>-3.738</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.1992</v>
+        <v>-5.5087</v>
       </c>
       <c r="I8" t="n">
-        <v>6.0435</v>
+        <v>1.771</v>
       </c>
       <c r="J8" t="n">
-        <v>14.5056</v>
+        <v>10.2022</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6645</v>
+        <v>3.5854</v>
       </c>
       <c r="L8" t="n">
-        <v>12.8411</v>
+        <v>6.6165</v>
       </c>
       <c r="M8" t="n">
-        <v>-14.6612</v>
+        <v>-13.94</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.863700000000001</v>
+        <v>-9.0937</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.7975</v>
+        <v>-4.8459</v>
       </c>
       <c r="P8" t="n">
-        <v>10.4404</v>
+        <v>0.0001999999999992841</v>
       </c>
       <c r="Q8" t="n">
-        <v>-18.7053</v>
+        <v>-36.1058</v>
       </c>
       <c r="R8" t="n">
-        <v>29.146</v>
+        <v>36.1058</v>
       </c>
       <c r="S8" t="n">
-        <v>3.8301</v>
+        <v>21.2937</v>
       </c>
       <c r="T8" t="n">
-        <v>6.6541</v>
+        <v>13.8477</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.824</v>
+        <v>7.4463</v>
       </c>
       <c r="V8" t="n">
-        <v>-11.4331</v>
+        <v>-23.9966</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.4583</v>
+        <v>5.6407</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.9749</v>
+        <v>-29.6375</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5884999999999998</v>
+        <v>-18.3405</v>
       </c>
       <c r="E9" t="n">
-        <v>20.2944</v>
+        <v>-2.5379</v>
       </c>
       <c r="F9" t="n">
-        <v>-19.7058</v>
+        <v>-15.8025</v>
       </c>
       <c r="G9" t="n">
-        <v>17.1242</v>
+        <v>-24.8459</v>
       </c>
       <c r="H9" t="n">
-        <v>-7.5001</v>
+        <v>-11.9783</v>
       </c>
       <c r="I9" t="n">
-        <v>24.6244</v>
+        <v>-12.8671</v>
       </c>
       <c r="J9" t="n">
-        <v>59.8297</v>
+        <v>15.1837</v>
       </c>
       <c r="K9" t="n">
-        <v>18.1386</v>
+        <v>8.7933</v>
       </c>
       <c r="L9" t="n">
-        <v>41.6913</v>
+        <v>6.3906</v>
       </c>
       <c r="M9" t="n">
-        <v>-42.7056</v>
+        <v>-40.0292</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.6386</v>
+        <v>-20.7716</v>
       </c>
       <c r="O9" t="n">
-        <v>-17.067</v>
+        <v>-19.2575</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.6977</v>
+        <v>-5.2202</v>
       </c>
       <c r="Q9" t="n">
-        <v>-59.8142</v>
+        <v>-57.4216</v>
       </c>
       <c r="R9" t="n">
-        <v>56.1171</v>
+        <v>52.2017</v>
       </c>
       <c r="S9" t="n">
-        <v>-16.6095</v>
+        <v>4.019</v>
       </c>
       <c r="T9" t="n">
-        <v>-7.8371</v>
+        <v>5.1329</v>
       </c>
       <c r="U9" t="n">
-        <v>-8.7721</v>
+        <v>-1.1137</v>
       </c>
       <c r="V9" t="n">
-        <v>3.7715</v>
+        <v>7.706100000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>28.1162</v>
+        <v>34.5678</v>
       </c>
       <c r="X9" t="n">
-        <v>-24.3444</v>
+        <v>-26.8612</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>C. JÜRGENS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>-20.4209</v>
+        <v>-18.4701</v>
       </c>
       <c r="E10" t="n">
-        <v>-16.8086</v>
+        <v>-20.2978</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.6123</v>
+        <v>1.8278</v>
       </c>
       <c r="G10" t="n">
-        <v>-18.2517</v>
+        <v>-18.2919</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1201000000000005</v>
+        <v>-2.844100000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-18.1317</v>
+        <v>-15.4479</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.0474</v>
+        <v>-8.875699999999998</v>
       </c>
       <c r="K10" t="n">
-        <v>7.417</v>
+        <v>3.599699999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.4644</v>
+        <v>-12.4755</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.204500000000001</v>
+        <v>-9.4162</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.5371</v>
+        <v>-6.4436</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6671000000000004</v>
+        <v>-2.9725</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6974</v>
+        <v>3.6976</v>
       </c>
       <c r="Q10" t="n">
-        <v>-13.0503</v>
+        <v>-26.9709</v>
       </c>
       <c r="R10" t="n">
-        <v>16.7477</v>
+        <v>30.6683</v>
       </c>
       <c r="S10" t="n">
-        <v>2.617999999999999</v>
+        <v>6.4373</v>
       </c>
       <c r="T10" t="n">
-        <v>6.4016</v>
+        <v>7.1035</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.7837</v>
+        <v>-0.6660999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-8.4848</v>
+        <v>-10.3128</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1124000000000001</v>
+        <v>8.4452</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.372300000000001</v>
+        <v>-18.758</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. JÜRGENS</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>-29.1217</v>
+        <v>-18.6729</v>
       </c>
       <c r="E11" t="n">
-        <v>-26.6646</v>
+        <v>-18.1172</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4571</v>
+        <v>-0.5555</v>
       </c>
       <c r="G11" t="n">
-        <v>-18.2919</v>
+        <v>-18.2517</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.844100000000001</v>
+        <v>-0.1201000000000005</v>
       </c>
       <c r="I11" t="n">
-        <v>-15.4479</v>
+        <v>-18.1317</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.875699999999998</v>
+        <v>-10.0474</v>
       </c>
       <c r="K11" t="n">
-        <v>3.599699999999999</v>
+        <v>7.417</v>
       </c>
       <c r="L11" t="n">
-        <v>-12.4755</v>
+        <v>-17.4644</v>
       </c>
       <c r="M11" t="n">
-        <v>-9.4162</v>
+        <v>-8.204500000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.4436</v>
+        <v>-7.5371</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.9725</v>
+        <v>-0.6671000000000004</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6976</v>
+        <v>3.6974</v>
       </c>
       <c r="Q11" t="n">
-        <v>-26.9709</v>
+        <v>-13.0503</v>
       </c>
       <c r="R11" t="n">
-        <v>30.6683</v>
+        <v>16.7477</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.2142</v>
+        <v>4.366</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7365999999999997</v>
+        <v>5.093</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.9511</v>
+        <v>-0.7270000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-10.3128</v>
+        <v>-8.4848</v>
       </c>
       <c r="W11" t="n">
-        <v>8.4452</v>
+        <v>-0.1124000000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-18.758</v>
+        <v>-8.372300000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. SARAIVA SEIXAS</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>-29.8218</v>
+        <v>-18.7312</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.988</v>
+        <v>7.918799999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.8339</v>
+        <v>-26.6494</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.2887</v>
+        <v>-18.5102</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.2192</v>
+        <v>-4.736499999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0692</v>
+        <v>-13.7741</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6473999999999995</v>
+        <v>13.538</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2773999999999999</v>
+        <v>10.9174</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3701000000000003</v>
+        <v>2.6202</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.936100000000001</v>
+        <v>-32.0488</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.4966</v>
+        <v>-15.6538</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.4397</v>
+        <v>-16.395</v>
       </c>
       <c r="P12" t="n">
-        <v>3.914899999999999</v>
+        <v>-8.917899999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-21.098</v>
+        <v>-45.8937</v>
       </c>
       <c r="R12" t="n">
-        <v>25.0127</v>
+        <v>36.9757</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.2595</v>
+        <v>11.9113</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.9208</v>
+        <v>11.5401</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6612</v>
+        <v>0.3709</v>
       </c>
       <c r="V12" t="n">
-        <v>-22.1885</v>
+        <v>-3.213799999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>5.3835</v>
+        <v>28.7342</v>
       </c>
       <c r="X12" t="n">
-        <v>-27.5722</v>
+        <v>-31.9481</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>D. SARAIVA SEIXAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>-37.555</v>
+        <v>-19.4251</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.2637</v>
+        <v>-11.5228</v>
       </c>
       <c r="F13" t="n">
-        <v>-22.291</v>
+        <v>-7.9022</v>
       </c>
       <c r="G13" t="n">
-        <v>-24.8459</v>
+        <v>-7.2887</v>
       </c>
       <c r="H13" t="n">
-        <v>-11.9783</v>
+        <v>-4.2192</v>
       </c>
       <c r="I13" t="n">
-        <v>-12.8671</v>
+        <v>-3.0692</v>
       </c>
       <c r="J13" t="n">
-        <v>15.1837</v>
+        <v>0.6473999999999995</v>
       </c>
       <c r="K13" t="n">
-        <v>8.7933</v>
+        <v>0.2773999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>6.3906</v>
+        <v>0.3701000000000003</v>
       </c>
       <c r="M13" t="n">
-        <v>-40.0292</v>
+        <v>-7.936100000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-20.7716</v>
+        <v>-4.4966</v>
       </c>
       <c r="O13" t="n">
-        <v>-19.2575</v>
+        <v>-3.4397</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.2202</v>
+        <v>3.914899999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-57.4216</v>
+        <v>-21.098</v>
       </c>
       <c r="R13" t="n">
-        <v>52.2017</v>
+        <v>25.0127</v>
       </c>
       <c r="S13" t="n">
-        <v>-15.1957</v>
+        <v>6.137</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.5929</v>
+        <v>3.5438</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.6023</v>
+        <v>2.593</v>
       </c>
       <c r="V13" t="n">
-        <v>7.706100000000001</v>
+        <v>-22.1885</v>
       </c>
       <c r="W13" t="n">
-        <v>34.5678</v>
+        <v>5.3835</v>
       </c>
       <c r="X13" t="n">
-        <v>-26.8612</v>
+        <v>-27.5722</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>-45.1443</v>
+        <v>-37.7993</v>
       </c>
       <c r="E14" t="n">
-        <v>-35.904</v>
+        <v>-30.1467</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.240500000000001</v>
+        <v>-7.652699999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-28.5668</v>
@@ -1546,13 +1546,13 @@
         <v>21.3156</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.6568</v>
+        <v>1.6882</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.481</v>
+        <v>2.2761</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.1755</v>
+        <v>-0.5876</v>
       </c>
       <c r="V14" t="n">
         <v>-10.7033</v>
@@ -1579,13 +1579,13 @@
         <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>-64.9552</v>
+        <v>-30.51430000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>31.08689999999999</v>
+        <v>43.87060000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>-96.04229999999998</v>
+        <v>-74.38369999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-104.9532</v>
@@ -1603,7 +1603,7 @@
         <v>75.45779999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>77.74560000000001</v>
+        <v>77.7456</v>
       </c>
       <c r="M15" t="n">
         <v>-258.158</v>
@@ -1618,22 +1618,22 @@
         <v>38.063</v>
       </c>
       <c r="Q15" t="n">
-        <v>-414.3478000000001</v>
+        <v>-414.3478</v>
       </c>
       <c r="R15" t="n">
         <v>452.4118</v>
       </c>
       <c r="S15" t="n">
-        <v>77.65979999999998</v>
+        <v>112.1013</v>
       </c>
       <c r="T15" t="n">
-        <v>89.98690000000001</v>
+        <v>102.7702</v>
       </c>
       <c r="U15" t="n">
-        <v>-12.3262</v>
+        <v>9.332100000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-75.72529999999999</v>
+        <v>-75.7253</v>
       </c>
       <c r="W15" t="n">
         <v>202.246</v>
